--- a/Fase 1/Evidencias Grupales/PLANILLA DE EVALUACIÓN FASE 1.xlsx
+++ b/Fase 1/Evidencias Grupales/PLANILLA DE EVALUACIÓN FASE 1.xlsx
@@ -23,6 +23,9 @@
     <t>INDICADOR DE EVALUACIÓN</t>
   </si>
   <si>
+    <t>INDICADORES DE EVALUACIÓN</t>
+  </si>
+  <si>
     <t>PONDERACIÓN</t>
   </si>
   <si>
@@ -32,40 +35,22 @@
     <t>1) Describe brevemente en qué consiste el Proyecto APT, justificando su relevancia para el campo laboral de su carrera.</t>
   </si>
   <si>
+    <t>1) Presenta el proyecto considerando la relevancia, objetivos, metodología y desarrollo, de acuerdo a los estándares de calidad de la disciplina. </t>
+  </si>
+  <si>
+    <t>2) Genera evidencias que dan cuenta del cumplimiento del Proyecto CAPSTONE, en relación a documentación, programación y almacenamiento de datos, de acuerdo a lo planificado por el equipo y que cumpla con estándares de desarrollo de la industria.</t>
+  </si>
+  <si>
     <t>2) Relaciona el Proyecto APT con las competencias del perfil de egreso de su Plan de Estudio.</t>
+  </si>
+  <si>
+    <t>2) Presenta las evidencias del Proyecto APT, dando cuenta del cumplimiento de los objetivos y de acuerdo a los estándares de la disciplina. </t>
   </si>
   <si>
     <t>3) Relaciona el Proyecto APT con sus intereses profesionales. *</t>
   </si>
   <si>
-    <t>4) Argumenta por qué el proyecto es factible de realizarse en el marco de la asignatura.</t>
-  </si>
-  <si>
-    <t>5) Formula objetivos claros, concisos y coherentes con la disciplina y la situación a abordar.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Inherit"/>
-        <color rgb="FF000000"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">2) </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Inherit"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>Genera evidencias que dan cuenta del cumplimiento del Proyecto CAPSTONE, en relación a documentación, programación y almacenamiento de datos, de acuerdo a lo planificado por el equipo y que cumpla con estándares de desarrollo de la industria.</t>
-    </r>
-  </si>
-  <si>
-    <t>6) Propone una metodología de trabajo que permite alcanzar los objetivos propuestos y es pertinente con los requerimientos disciplinares.</t>
-  </si>
-  <si>
-    <t>7) Establece un plan de trabajo para su proyecto APT considerando los recursos, duración, facilitadores y obstaculizadores en el desarrollo de las actividades.</t>
+    <t>3) Responde las preguntas realizadas por la comisión, cumpliendo con los estándares de calidad de la disciplina.</t>
   </si>
   <si>
     <r>
@@ -86,7 +71,10 @@
     </r>
   </si>
   <si>
-    <t>8) Determina evidencias, justificando cómo estas dan cuenta del logro de las actividades del Proyecto APT.</t>
+    <t>4) Argumenta por qué el proyecto es factible de realizarse en el marco de la asignatura.</t>
+  </si>
+  <si>
+    <t>4) Expone el Proyecto APT, considerando el formato y el tiempo establecido para la presentación.</t>
   </si>
   <si>
     <r>
@@ -107,7 +95,10 @@
     </r>
   </si>
   <si>
-    <t>9) Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias.</t>
+    <t>5) Formula objetivos claros, concisos y coherentes con la disciplina y la situación a abordar.</t>
+  </si>
+  <si>
+    <t>5) Expresa sus ideas con fluidez, claridad y precisión, utilizando lenguaje técnico propio de la disciplina.</t>
   </si>
   <si>
     <r>
@@ -128,7 +119,79 @@
     </r>
   </si>
   <si>
+    <t>6) Propone una metodología de trabajo que permite alcanzar los objetivos propuestos y es pertinente con los requerimientos disciplinares.</t>
+  </si>
+  <si>
     <t>6) Utiliza correctamente las reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </t>
+  </si>
+  <si>
+    <t>7) Establece un plan de trabajo para su proyecto APT considerando los recursos, duración, facilitadores y obstaculizadores en el desarrollo de las actividades.</t>
+  </si>
+  <si>
+    <t>7) Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estructura y nombres solicitados, guardando todas las evidencias de avances en Git.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Inherit"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">6) </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Inherit"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estructura y nombres solicitados, guardando todas las evidencias de avances en Git.</t>
+    </r>
+  </si>
+  <si>
+    <t>8) Determina evidencias, justificando cómo estas dan cuenta del logro de las actividades del Proyecto APT.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Inherit"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">8) </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Inherit"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</t>
+    </r>
+  </si>
+  <si>
+    <t>9) Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Inherit"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>7) </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Inherit"/>
+        <color theme="1"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</t>
+    </r>
+  </si>
+  <si>
+    <t>9) Generan evidencias claras dentro del repositorio del aporte de cada uno de los integrantes del equipo que permitan identificar la equidad en el trabajo y la participación de cada estudiante.</t>
   </si>
   <si>
     <r>
@@ -157,49 +220,10 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Inherit"/>
-        <color rgb="FF000000"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">7) </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Inherit"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estructura y nombres solicitados, guardando todas las evidencias de avances en Git.</t>
-    </r>
+    <t>10) Colaboración y trabajo en equipo. *</t>
   </si>
   <si>
     <t>11) Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información.*</t>
-  </si>
-  <si>
-    <t>INDICADORES DE EVALUACIÓN</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Inherit"/>
-        <color rgb="FF000000"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">8) </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Inherit"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</t>
-    </r>
-  </si>
-  <si>
-    <t>9) Generan evidencias claras dentro del repositorio del aporte de cada uno de los integrantes del equipo que permitan identificar la equidad en el trabajo y la participación de cada estudiante.</t>
   </si>
   <si>
     <r>
@@ -228,12 +252,6 @@
     </r>
   </si>
   <si>
-    <t>10) Colaboración y trabajo en equipo. *</t>
-  </si>
-  <si>
-    <t>1) Presenta el proyecto considerando la relevancia, objetivos, metodología y desarrollo, de acuerdo a los estándares de calidad de la disciplina. </t>
-  </si>
-  <si>
     <r>
       <rPr>
         <rFont val="Inherit"/>
@@ -251,60 +269,12 @@
       <t> Colaboración y trabajo en equipo. *</t>
     </r>
   </si>
-  <si>
-    <t>2) Presenta las evidencias del Proyecto APT, dando cuenta del cumplimiento de los objetivos y de acuerdo a los estándares de la disciplina. </t>
-  </si>
-  <si>
-    <t>3) Responde las preguntas realizadas por la comisión, cumpliendo con los estándares de calidad de la disciplina.</t>
-  </si>
-  <si>
-    <t>4) Expone el Proyecto APT, considerando el formato y el tiempo establecido para la presentación.</t>
-  </si>
-  <si>
-    <t>5) Expresa sus ideas con fluidez, claridad y precisión, utilizando lenguaje técnico propio de la disciplina.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Inherit"/>
-        <color rgb="FF000000"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t xml:space="preserve">6) </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Inherit"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estructura y nombres solicitados, guardando todas las evidencias de avances en Git.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Inherit"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>7) </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Inherit"/>
-        <color theme="1"/>
-        <sz val="11.0"/>
-      </rPr>
-      <t>Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</t>
-    </r>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -338,6 +308,11 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -353,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -372,11 +347,14 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -610,12 +588,12 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="5">
         <v>0.1</v>
@@ -623,7 +601,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3" s="5">
         <v>0.05</v>
@@ -631,7 +609,7 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" s="5">
         <v>0.1</v>
@@ -639,7 +617,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B5" s="5">
         <v>0.05</v>
@@ -647,7 +625,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5">
         <v>0.05</v>
@@ -655,7 +633,7 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B7" s="5">
         <v>0.1</v>
@@ -663,7 +641,7 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B8" s="5">
         <v>0.1</v>
@@ -671,7 +649,7 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B9" s="5">
         <v>0.05</v>
@@ -679,7 +657,7 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B10" s="5">
         <v>0.05</v>
@@ -687,7 +665,7 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B11" s="5">
         <v>0.05</v>
@@ -695,7 +673,7 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5">
         <v>0.1</v>
@@ -703,22 +681,22 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B13" s="4">
         <v>0.1</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="6" t="s">
-        <v>26</v>
+      <c r="A14" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="B14" s="4">
         <v>0.1</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="B15" s="7">
+      <c r="B15" s="6">
         <f>SUM(B2:B14)</f>
         <v>1</v>
       </c>
@@ -1733,20 +1711,20 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4">
         <v>0.1</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
+      <c r="A3" s="7" t="s">
+        <v>6</v>
       </c>
       <c r="B3" s="4">
         <v>0.2</v>
@@ -1762,7 +1740,7 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="4">
         <v>0.05</v>
@@ -1770,7 +1748,7 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="4">
         <v>0.05</v>
@@ -1778,15 +1756,15 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B7" s="4">
         <v>0.05</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>18</v>
+      <c r="A8" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="B8" s="4">
         <v>0.15</v>
@@ -1794,30 +1772,30 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B9" s="4">
         <v>0.1</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="6" t="s">
-        <v>22</v>
+      <c r="A10" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="B10" s="4">
         <v>0.15</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="6" t="s">
-        <v>24</v>
+      <c r="A11" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="B11" s="4">
         <v>0.1</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <f>SUM(B2:B11)</f>
         <v>1</v>
       </c>
@@ -2831,76 +2809,76 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="7">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6">
         <v>0.15</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="7">
+        <v>8</v>
+      </c>
+      <c r="B3" s="6">
         <v>0.25</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="7">
+        <v>10</v>
+      </c>
+      <c r="B4" s="6">
         <v>0.2</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="7">
+        <v>13</v>
+      </c>
+      <c r="B5" s="6">
         <v>0.05</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="7">
+        <v>16</v>
+      </c>
+      <c r="B6" s="6">
         <v>0.05</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="7">
+        <v>22</v>
+      </c>
+      <c r="B7" s="6">
         <v>0.2</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="7">
+      <c r="A8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="6">
         <v>0.1</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <f>SUM(B2:B8)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="B10" s="8"/>
+      <c r="B10" s="9"/>
     </row>
     <row r="11" ht="14.25" customHeight="1"/>
     <row r="12" ht="14.25" customHeight="1"/>
